--- a/weather.xlsx
+++ b/weather.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,426 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C6" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>04/07/2026, 11:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D7" t="n">
+        <v>64</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>04/07/2026, 11:58:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D8" t="n">
+        <v>64</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>04/07/2026, 11:58:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C9" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D9" t="n">
+        <v>64</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>04/07/2026, 11:58:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D10" t="n">
+        <v>64</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>04/07/2026, 11:58:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D11" t="n">
+        <v>64</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>04/07/2026, 11:58:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="C12" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="D12" t="n">
+        <v>64</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>04/07/2026, 11:58:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dąbrowa Górnicza</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="C13" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="D13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>04:38:17</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>20:56:12</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>broken clouds</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>04/07/2026, 12:09:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>62</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>04:21:00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>20:59:18</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>overcast clouds</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>04/07/2026, 12:10:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Warsaw</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="C15" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="D15" t="n">
+        <v>62</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>04:21:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>20:59:18</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>overcast clouds</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>04/07/2026, 12:27:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
